--- a/app/analysis/results.xlsx
+++ b/app/analysis/results.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="RAW" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="STATS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="statistic_tests" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -443,11 +444,15 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
-    <col width="33" customWidth="1" min="11" max="11"/>
-    <col width="39" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
+    <col width="33" customWidth="1" min="14" max="14"/>
+    <col width="49" customWidth="1" min="15" max="15"/>
+    <col width="39" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,25 +498,45 @@
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
+          <t>turns geo</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
           <t>token math</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>turns math</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>pairs resolved from geo robot</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>pairs resolved from geo robot based on tokens</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>pairs resolved from math robot</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>pairs resolved from math robot based on tokens</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>number of curiosities from geo robot</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>number of curiosities from math robot</t>
         </is>
@@ -545,523 +570,667 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="J2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3" t="n">
+      <c r="L2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="O2" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P2" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="Q2" s="3" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>CS0</t>
+          <t>CS1</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M3" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q3" s="3" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>CS1</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>102</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3" t="n">
+      <c r="J4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q4" s="3" t="n">
         <v>7</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="J5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>CI</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="E5" s="3" t="n">
+      <c r="K5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>7</v>
+      <c r="Q5" s="3" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>260</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>36</v>
+        <v>0.33</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>CS0</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>135</v>
+        <v>63</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="n">
         <v>12</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>CS0</t>
+          <t>CS1</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>8</v>
+        <v>0.33</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>CS1</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>88</v>
+        <v>170</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>4</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="3" t="n">
         <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>CI</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>170</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="E11" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P11" s="3" t="n">
         <v>9</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>CS0</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>107</v>
-      </c>
-      <c r="E12" s="3" t="n">
+      <c r="Q12" s="3" t="n">
         <v>13</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>CS0</t>
+          <t>CS1</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>CS1</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>137</v>
+        <v>61</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>0</v>
@@ -1070,29 +1239,41 @@
         <v>0</v>
       </c>
       <c r="L14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="M14" s="3" t="n">
-        <v>19</v>
+      <c r="Q14" s="3" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>0</v>
@@ -1113,69 +1294,93 @@
         <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="3" t="n">
         <v>9</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>9</v>
+        <v>0.5</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>CS0</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>13</v>
@@ -1184,196 +1389,916 @@
         <v>0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>10</v>
+        <v>0.5</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>CS0</t>
+          <t>CS1</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q18" s="3" t="n">
         <v>9</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="E19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>CS1</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="F19" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M19" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3" t="n">
         <v>9</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>137</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>CS0</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>CS1</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>137</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>CS0</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>CS1</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>209</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>283</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="P30" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3" t="n">
+      <c r="Q30" s="3" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>199</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="Q31" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>CS0</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>CS1</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>152</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q33" s="3" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1388,7 +2313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1404,16 +2329,24 @@
     <col width="26" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
-    <col width="36" customWidth="1" min="16" max="16"/>
-    <col width="36" customWidth="1" min="17" max="17"/>
-    <col width="37" customWidth="1" min="18" max="18"/>
-    <col width="37" customWidth="1" min="19" max="19"/>
-    <col width="43" customWidth="1" min="20" max="20"/>
-    <col width="43" customWidth="1" min="21" max="21"/>
-    <col width="44" customWidth="1" min="22" max="22"/>
-    <col width="44" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
+    <col width="52" customWidth="1" min="22" max="22"/>
+    <col width="52" customWidth="1" min="23" max="23"/>
+    <col width="37" customWidth="1" min="24" max="24"/>
+    <col width="37" customWidth="1" min="25" max="25"/>
+    <col width="53" customWidth="1" min="26" max="26"/>
+    <col width="53" customWidth="1" min="27" max="27"/>
+    <col width="43" customWidth="1" min="28" max="28"/>
+    <col width="43" customWidth="1" min="29" max="29"/>
+    <col width="44" customWidth="1" min="30" max="30"/>
+    <col width="44" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1484,50 +2417,90 @@
       </c>
       <c r="N1" s="2" t="inlineStr">
         <is>
+          <t>turns geo_avg</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>turns geo_std</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
           <t>token math_avg</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>token math_std</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>turns math_avg</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>turns math_std</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>pairs resolved from geo robot_avg</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>pairs resolved from geo robot_std</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>pairs resolved from geo robot based on tokens_avg</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>pairs resolved from geo robot based on tokens_std</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>pairs resolved from math robot_avg</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>pairs resolved from math robot_std</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>pairs resolved from math robot based on tokens_avg</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>pairs resolved from math robot based on tokens_std</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t>number of curiosities from geo robot_avg</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t>number of curiosities from geo robot_std</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t>number of curiosities from math robot_avg</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="AE1" s="2" t="inlineStr">
         <is>
           <t>number of curiosities from math robot_std</t>
         </is>
@@ -1540,22 +2513,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>49.5</v>
+        <v>45.71</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>12.26</v>
+        <v>11.51</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>110.75</v>
+        <v>124.29</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>18.19</v>
+        <v>37.81</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>13.25</v>
+        <v>15</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>2.06</v>
+        <v>4.58</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0</v>
@@ -1564,46 +2537,70 @@
         <v>0</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>3</v>
+        <v>1.14</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>2.58</v>
+        <v>1.21</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>6.75</v>
+        <v>2.29</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>2.99</v>
+        <v>2.43</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.75</v>
+        <v>2.43</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.96</v>
+        <v>1.72</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>2.25</v>
+        <v>4.57</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>1.71</v>
+        <v>3.64</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>10.75</v>
+        <v>0.71</v>
       </c>
       <c r="U2" s="3" t="n">
-        <v>3.1</v>
+        <v>0.95</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>10.25</v>
+        <v>0.19</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>2.36</v>
+        <v>0.24</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA2" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB2" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC2" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AD2" s="3" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>4.46</v>
       </c>
     </row>
     <row r="3">
@@ -1613,70 +2610,94 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>54</v>
+        <v>54.33</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>19.39</v>
+        <v>17.13</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>131.5</v>
+        <v>139.17</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>48.23</v>
+        <v>52.2</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6.16</v>
+        <v>6.69</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="J3" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>3.75</v>
+        <v>2.33</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>2.99</v>
+        <v>1.37</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>3.3</v>
+        <v>2.37</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.5</v>
+        <v>2.17</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.58</v>
+        <v>1.33</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>4.9</v>
+        <v>0.89</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>12.5</v>
+        <v>0.23</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>5.92</v>
+        <v>0.21</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC3" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>6.78</v>
       </c>
     </row>
     <row r="4">
@@ -1686,22 +2707,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>46</v>
+        <v>41.67</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>10.58</v>
+        <v>11.83</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>95.5</v>
+        <v>99.83</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>30.62</v>
+        <v>32.13</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>3.87</v>
+        <v>4.1</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>0</v>
@@ -1710,46 +2731,70 @@
         <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="K4" s="3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T4" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="L4" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P4" s="3" t="n">
+      <c r="U4" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="W4" s="3" t="n">
         <v>0.25</v>
       </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>3.2</v>
+      <c r="X4" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AA4" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AB4" s="3" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="AC4" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>3.27</v>
       </c>
     </row>
     <row r="5">
@@ -1759,70 +2804,94 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>45.5</v>
+        <v>42.57</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>8.23</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102.5</v>
+        <v>106.57</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>24.37</v>
+        <v>32.29</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>3.11</v>
+        <v>4.2</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2.75</v>
+        <v>2.14</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>4.25</v>
+        <v>2.71</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>2.22</v>
+        <v>1.11</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>5.75</v>
+        <v>4.86</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.75</v>
+        <v>2.86</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.25</v>
+        <v>5.57</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.5</v>
+        <v>1.81</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>7</v>
+        <v>0.86</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>3.16</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>14.75</v>
+        <v>0.2</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>4.65</v>
+        <v>0.18</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA5" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AB5" s="3" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="AC5" s="3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD5" s="3" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>4.34</v>
       </c>
     </row>
     <row r="6">
@@ -1832,70 +2901,394 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>52.5</v>
+        <v>60.67</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>30.22</v>
+        <v>26.61</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>121</v>
+        <v>150.67</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>99.53</v>
+        <v>100.93</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>14.75</v>
+        <v>18.5</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>12.26</v>
+        <v>12.5</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>1.15</v>
+        <v>0.98</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>2.83</v>
+        <v>2.42</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>7.72</v>
+        <v>3.27</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>2.5</v>
+        <v>4.83</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>3.79</v>
+        <v>6.4</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.5</v>
+        <v>1.64</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>10.75</v>
+        <v>0.17</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>5.62</v>
+        <v>0.41</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>16.75</v>
+        <v>0.01</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>12.97</v>
+        <v>0.03</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AA6" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AB6" s="3" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="AC6" s="3" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="AD6" s="3" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="AE6" s="3" t="n">
+        <v>10.29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Variabile</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Test Utilizzato</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Statistica</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>p-value</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Significativo (p&lt;0.05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>turns</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Welch ANOVA</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1.065480843914207</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.414083030778958</v>
+      </c>
+      <c r="E2" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>time to finish_sec</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Welch ANOVA</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0.7618775847333288</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.5692227716293521</v>
+      </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>avg_find_pair_sec</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Welch ANOVA</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0.7530468399732498</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0.5744397965820626</v>
+      </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>board changed times</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0.6941706238742428</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.6027692231766846</v>
+      </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>token geo</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Kruskal-Wallis</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>6.590323354011216</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.1591875074880585</v>
+      </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>turns geo</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Kruskal-Wallis</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>5.415110004151106</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.2472927622910715</v>
+      </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>token math</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1.270635565069757</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0.3068243800011841</v>
+      </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>turns math</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Kruskal-Wallis</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>4.410159716060337</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0.3533335203450358</v>
+      </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>pairs resolved from geo robot</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Kruskal-Wallis</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>4.814217032967021</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0.3068965596953456</v>
+      </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>pairs resolved from math robot</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Kruskal-Wallis</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>9.69474789915963</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0.04589581756624762</v>
+      </c>
+      <c r="E11" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>board changed times</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0.6941706238742428</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0.6027692231766846</v>
+      </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>wrong moves</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Kruskal-Wallis</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>14.07972997628167</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0.007044890352619388</v>
+      </c>
+      <c r="E13" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/app/analysis/results.xlsx
+++ b/app/analysis/results.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2300,6 +2300,116 @@
       </c>
       <c r="Q33" s="3" t="n">
         <v>13</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q34" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2610,70 +2720,70 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>54.33</v>
+        <v>51.14</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>17.13</v>
+        <v>17.77</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>139.17</v>
+        <v>134.71</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>52.2</v>
+        <v>49.08</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>17</v>
+        <v>16.43</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6.69</v>
+        <v>6.29</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>4</v>
+        <v>4.43</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="R3" s="3" t="n">
         <v>4</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>2.61</v>
+        <v>2.38</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="X3" s="3" t="n">
         <v>0</v>
@@ -2688,16 +2798,16 @@
         <v>0</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>12</v>
+        <v>11.57</v>
       </c>
       <c r="AC3" s="3" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>14</v>
+        <v>12.71</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>6.78</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="4">
@@ -2901,94 +3011,94 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>60.67</v>
+        <v>59.43</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>26.61</v>
+        <v>24.51</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>150.67</v>
+        <v>152</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>100.93</v>
+        <v>92.2</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>18.5</v>
+        <v>18.71</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>12.5</v>
+        <v>11.43</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.83</v>
+        <v>1.57</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.98</v>
+        <v>2.15</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>3.27</v>
+        <v>3.04</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>4.83</v>
+        <v>5.29</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>6.4</v>
+        <v>5.96</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>3</v>
+        <v>3.86</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>3.29</v>
+        <v>3.76</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>0.01</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AA6" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>12.67</v>
+        <v>12.71</v>
       </c>
       <c r="AC6" s="3" t="n">
-        <v>5.72</v>
+        <v>5.22</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>15.33</v>
+        <v>14</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>10.29</v>
+        <v>10.03</v>
       </c>
     </row>
   </sheetData>
@@ -3008,7 +3118,7 @@
     <col width="33" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -3047,14 +3157,14 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Welch ANOVA</t>
+          <t>ANOVA</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1.065480843914207</v>
+        <v>1.337939864894698</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.414083030778958</v>
+        <v>0.2805207333575773</v>
       </c>
       <c r="E2" s="3" t="b">
         <v>0</v>
@@ -3068,14 +3178,14 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Welch ANOVA</t>
+          <t>ANOVA</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.7618775847333288</v>
+        <v>1.122995758715891</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.5692227716293521</v>
+        <v>0.3656161163140317</v>
       </c>
       <c r="E3" s="3" t="b">
         <v>0</v>
@@ -3089,14 +3199,14 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Welch ANOVA</t>
+          <t>ANOVA</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.7530468399732498</v>
+        <v>1.15817425853639</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.5744397965820626</v>
+        <v>0.3502515003752136</v>
       </c>
       <c r="E4" s="3" t="b">
         <v>0</v>
@@ -3114,10 +3224,10 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.6941706238742428</v>
+        <v>0.6071726438698914</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.6027692231766846</v>
+        <v>0.6607756463378074</v>
       </c>
       <c r="E5" s="3" t="b">
         <v>0</v>
@@ -3135,10 +3245,10 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>6.590323354011216</v>
+        <v>7.014537208822923</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.1591875074880585</v>
+        <v>0.1351219918410739</v>
       </c>
       <c r="E6" s="3" t="b">
         <v>0</v>
@@ -3156,10 +3266,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5.415110004151106</v>
+        <v>5.763748185125363</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.2472927622910715</v>
+        <v>0.2175000840549547</v>
       </c>
       <c r="E7" s="3" t="b">
         <v>0</v>
@@ -3177,10 +3287,10 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1.270635565069757</v>
+        <v>0.8408139253209675</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.3068243800011841</v>
+        <v>0.511071729103067</v>
       </c>
       <c r="E8" s="3" t="b">
         <v>0</v>
@@ -3198,10 +3308,10 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>4.410159716060337</v>
+        <v>3.391038530070464</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.3533335203450358</v>
+        <v>0.4946383437950717</v>
       </c>
       <c r="E9" s="3" t="b">
         <v>0</v>
@@ -3219,10 +3329,10 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.814217032967021</v>
+        <v>6.140360906267262</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.3068965596953456</v>
+        <v>0.1889083849266484</v>
       </c>
       <c r="E10" s="3" t="b">
         <v>0</v>
@@ -3240,10 +3350,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>9.69474789915963</v>
+        <v>10.71897510273144</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.04589581756624762</v>
+        <v>0.02991067763056201</v>
       </c>
       <c r="E11" s="3" t="b">
         <v>1</v>
@@ -3261,10 +3371,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.6941706238742428</v>
+        <v>0.6071726438698914</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.6027692231766846</v>
+        <v>0.6607756463378074</v>
       </c>
       <c r="E12" s="3" t="b">
         <v>0</v>
@@ -3282,10 +3392,10 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>14.07972997628167</v>
+        <v>13.25790987535952</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.007044890352619388</v>
+        <v>0.01008199550361754</v>
       </c>
       <c r="E13" s="3" t="b">
         <v>1</v>

--- a/app/analysis/results.xlsx
+++ b/app/analysis/results.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2410,6 +2410,336 @@
       </c>
       <c r="Q35" s="3" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>CS0</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>CS1</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>249</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2623,22 +2953,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>45.71</v>
+        <v>42.89</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>11.51</v>
+        <v>11.54</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>124.29</v>
+        <v>119.78</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>37.81</v>
+        <v>36.72</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>15</v>
+        <v>14.44</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>4.58</v>
+        <v>4.48</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0</v>
@@ -2647,52 +2977,52 @@
         <v>0</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>2.43</v>
+        <v>2.24</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>4.57</v>
+        <v>3.78</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>3.64</v>
+        <v>3.56</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="U2" s="3" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="X2" s="3" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="Z2" s="3" t="n">
         <v>0.24</v>
@@ -2701,16 +3031,16 @@
         <v>0.25</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>11</v>
+        <v>10.22</v>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>2.31</v>
+        <v>2.54</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>10.71</v>
+        <v>10.22</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>4.46</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="3">
@@ -2720,70 +3050,70 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>51.14</v>
+        <v>50.75</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>17.77</v>
+        <v>16.49</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>134.71</v>
+        <v>142.88</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>49.08</v>
+        <v>50.97</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>16.43</v>
+        <v>17.5</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6.29</v>
+        <v>6.57</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>4.43</v>
+        <v>5.12</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="R3" s="3" t="n">
         <v>4</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="X3" s="3" t="n">
         <v>0</v>
@@ -2798,16 +3128,16 @@
         <v>0</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>11.57</v>
+        <v>10.62</v>
       </c>
       <c r="AC3" s="3" t="n">
-        <v>3.91</v>
+        <v>4.5</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>12.71</v>
+        <v>13.12</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>7.06</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="4">
@@ -2817,22 +3147,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>41.67</v>
+        <v>41.43</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>11.83</v>
+        <v>10.81</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>99.83</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>32.13</v>
+        <v>30.58</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>12</v>
+        <v>11.57</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>0</v>
@@ -2841,70 +3171,70 @@
         <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>0.25</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="AA4" s="3" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="AB4" s="3" t="n">
-        <v>9.83</v>
+        <v>9.43</v>
       </c>
       <c r="AC4" s="3" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>7.5</v>
+        <v>7.86</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>3.27</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="5">
@@ -2914,94 +3244,94 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>42.57</v>
+        <v>42.5</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>9.359999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>106.57</v>
+        <v>109.88</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>32.29</v>
+        <v>31.33</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>13</v>
+        <v>13.38</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>4.2</v>
+        <v>4.03</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>5.57</v>
+        <v>5.38</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="AA5" s="3" t="n">
         <v>0.06</v>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>7.57</v>
+        <v>7.5</v>
       </c>
       <c r="AC5" s="3" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>13.86</v>
+        <v>13.25</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>4.34</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="6">
@@ -3011,64 +3341,64 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>59.43</v>
+        <v>60</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>24.51</v>
+        <v>22.75</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>152</v>
+        <v>164.12</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>92.2</v>
+        <v>92</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>18.71</v>
+        <v>20.25</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>11.43</v>
+        <v>11.44</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>2.23</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>2.71</v>
+        <v>3.12</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>3.04</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>5.29</v>
+        <v>6.12</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>5.96</v>
+        <v>6.01</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>3.86</v>
+        <v>4.75</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>3.76</v>
+        <v>4.3</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>0.01</v>
@@ -3077,10 +3407,10 @@
         <v>0.02</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>0.02</v>
@@ -3089,16 +3419,16 @@
         <v>0.06</v>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>12.71</v>
+        <v>12.88</v>
       </c>
       <c r="AC6" s="3" t="n">
-        <v>5.22</v>
+        <v>4.85</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>10.03</v>
+        <v>9.32</v>
       </c>
     </row>
   </sheetData>
@@ -3117,8 +3447,8 @@
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -3157,14 +3487,14 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>ANOVA</t>
+          <t>Welch ANOVA</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1.337939864894698</v>
+        <v>1.317313190708848</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.2805207333575773</v>
+        <v>0.3042998957904168</v>
       </c>
       <c r="E2" s="3" t="b">
         <v>0</v>
@@ -3178,14 +3508,14 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ANOVA</t>
+          <t>Welch ANOVA</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1.122995758715891</v>
+        <v>1.644909255824071</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.3656161163140317</v>
+        <v>0.2104190874018795</v>
       </c>
       <c r="E3" s="3" t="b">
         <v>0</v>
@@ -3199,14 +3529,14 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>ANOVA</t>
+          <t>Welch ANOVA</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1.15817425853639</v>
+        <v>1.677105147035296</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.3502515003752136</v>
+        <v>0.2030586993161449</v>
       </c>
       <c r="E4" s="3" t="b">
         <v>0</v>
@@ -3220,14 +3550,14 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>ANOVA</t>
+          <t>Welch ANOVA</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.6071726438698914</v>
+        <v>1.55901690005224</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.6607756463378074</v>
+        <v>0.2311011063970209</v>
       </c>
       <c r="E5" s="3" t="b">
         <v>0</v>
@@ -3245,13 +3575,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>7.014537208822923</v>
+        <v>9.496670544196377</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.1351219918410739</v>
+        <v>0.0498157053047935</v>
       </c>
       <c r="E6" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3266,10 +3596,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5.763748185125363</v>
+        <v>8.281054860088346</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.2175000840549547</v>
+        <v>0.08180869517887805</v>
       </c>
       <c r="E7" s="3" t="b">
         <v>0</v>
@@ -3283,14 +3613,14 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>ANOVA</t>
+          <t>Kruskal-Wallis</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.8408139253209675</v>
+        <v>3.145427618139728</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.511071729103067</v>
+        <v>0.533790141635227</v>
       </c>
       <c r="E8" s="3" t="b">
         <v>0</v>
@@ -3308,10 +3638,10 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3.391038530070464</v>
+        <v>3.382541500565241</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.4946383437950717</v>
+        <v>0.4959613541370369</v>
       </c>
       <c r="E9" s="3" t="b">
         <v>0</v>
@@ -3329,10 +3659,10 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6.140360906267262</v>
+        <v>8.501604050711201</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.1889083849266484</v>
+        <v>0.0748386217510883</v>
       </c>
       <c r="E10" s="3" t="b">
         <v>0</v>
@@ -3350,10 +3680,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>10.71897510273144</v>
+        <v>12.31515583821576</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.02991067763056201</v>
+        <v>0.01515528027390947</v>
       </c>
       <c r="E11" s="3" t="b">
         <v>1</v>
@@ -3367,14 +3697,14 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>ANOVA</t>
+          <t>Welch ANOVA</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.6071726438698914</v>
+        <v>1.55901690005224</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.6607756463378074</v>
+        <v>0.2311011063970209</v>
       </c>
       <c r="E12" s="3" t="b">
         <v>0</v>
@@ -3392,10 +3722,10 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>13.25790987535952</v>
+        <v>17.67933354192744</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.01008199550361754</v>
+        <v>0.001425482501238332</v>
       </c>
       <c r="E13" s="3" t="b">
         <v>1</v>

--- a/app/analysis/results.xlsx
+++ b/app/analysis/results.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2740,6 +2740,281 @@
       </c>
       <c r="Q41" s="3" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>CS0</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>CS1</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q44" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q45" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2953,22 +3228,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>42.89</v>
+        <v>41.4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>11.54</v>
+        <v>11.85</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>119.78</v>
+        <v>116</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>36.72</v>
+        <v>36.62</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>14.44</v>
+        <v>14</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>4.48</v>
+        <v>4.45</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0</v>
@@ -2977,70 +3252,70 @@
         <v>0</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>2.24</v>
+        <v>2.41</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>3.56</v>
+        <v>3.43</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="U2" s="3" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="X2" s="3" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="AA2" s="3" t="n">
         <v>0.25</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>10.22</v>
+        <v>10</v>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>10.22</v>
+        <v>10</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>4.06</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="3">
@@ -3050,94 +3325,94 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>50.75</v>
+        <v>50.89</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>16.49</v>
+        <v>15.43</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>142.88</v>
+        <v>139.11</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>50.97</v>
+        <v>49</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6.57</v>
+        <v>6.32</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>5.12</v>
+        <v>4.67</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="W3" s="3" t="n">
         <v>0.18</v>
       </c>
       <c r="X3" s="3" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AA3" s="3" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>10.62</v>
+        <v>10.22</v>
       </c>
       <c r="AC3" s="3" t="n">
-        <v>4.5</v>
+        <v>4.38</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>13.12</v>
+        <v>13.33</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>6.64</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="4">
@@ -3147,22 +3422,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>41.43</v>
+        <v>40.5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>10.81</v>
+        <v>10.35</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>96.56999999999999</v>
+        <v>97.38</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>30.58</v>
+        <v>28.4</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>11.57</v>
+        <v>11.62</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>3.91</v>
+        <v>3.62</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>0</v>
@@ -3171,70 +3446,70 @@
         <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.76</v>
+        <v>0.71</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>1.07</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="V4" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W4" s="3" t="n">
         <v>0.24</v>
       </c>
-      <c r="W4" s="3" t="n">
-        <v>0.25</v>
-      </c>
       <c r="X4" s="3" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AA4" s="3" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="AB4" s="3" t="n">
-        <v>9.43</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AC4" s="3" t="n">
-        <v>3.46</v>
+        <v>3.56</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>7.86</v>
+        <v>8.75</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>3.13</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="5">
@@ -3244,76 +3519,76 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>42.5</v>
+        <v>42.44</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>8.67</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>109.88</v>
+        <v>111.67</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>31.33</v>
+        <v>29.79</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>13.38</v>
+        <v>13.56</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>4.03</v>
+        <v>3.81</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.89</v>
+        <v>0.83</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>5.38</v>
+        <v>5.44</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>0.03</v>
@@ -3322,16 +3597,16 @@
         <v>0.06</v>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>7.5</v>
+        <v>7.56</v>
       </c>
       <c r="AC5" s="3" t="n">
-        <v>2.67</v>
+        <v>2.51</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>13.25</v>
+        <v>13.22</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>4.37</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="6">
@@ -3341,64 +3616,64 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>60</v>
+        <v>65.11</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>22.75</v>
+        <v>26.23</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>164.12</v>
+        <v>168.11</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>92</v>
+        <v>86.88</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>20.25</v>
+        <v>20.78</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>11.44</v>
+        <v>10.81</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2.88</v>
+        <v>3.33</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>6.12</v>
+        <v>6.67</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>6.01</v>
+        <v>5.85</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>4.75</v>
+        <v>4.78</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>4.3</v>
+        <v>4.02</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>0.01</v>
@@ -3407,10 +3682,10 @@
         <v>0.02</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>0.02</v>
@@ -3419,16 +3694,16 @@
         <v>0.06</v>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>12.88</v>
+        <v>13.56</v>
       </c>
       <c r="AC6" s="3" t="n">
-        <v>4.85</v>
+        <v>4.98</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>13.75</v>
+        <v>14.67</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>9.32</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3448,7 +3723,7 @@
     <col width="33" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -3491,10 +3766,10 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1.317313190708848</v>
+        <v>2.067175831394276</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.3042998957904168</v>
+        <v>0.1253990966241199</v>
       </c>
       <c r="E2" s="3" t="b">
         <v>0</v>
@@ -3512,10 +3787,10 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1.644909255824071</v>
+        <v>2.030109204962793</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.2104190874018795</v>
+        <v>0.1307841068053283</v>
       </c>
       <c r="E3" s="3" t="b">
         <v>0</v>
@@ -3533,10 +3808,10 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1.677105147035296</v>
+        <v>2.10597923163696</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.2030586993161449</v>
+        <v>0.1200168571318576</v>
       </c>
       <c r="E4" s="3" t="b">
         <v>0</v>
@@ -3550,14 +3825,14 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Welch ANOVA</t>
+          <t>Kruskal-Wallis</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1.55901690005224</v>
+        <v>7.455225220291108</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.2311011063970209</v>
+        <v>0.1136999556090968</v>
       </c>
       <c r="E5" s="3" t="b">
         <v>0</v>
@@ -3571,14 +3846,14 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Kruskal-Wallis</t>
+          <t>Welch ANOVA</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>9.496670544196377</v>
+        <v>4.175921966613092</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.0498157053047935</v>
+        <v>0.01339961772467672</v>
       </c>
       <c r="E6" s="3" t="b">
         <v>1</v>
@@ -3592,17 +3867,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Kruskal-Wallis</t>
+          <t>Welch ANOVA</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8.281054860088346</v>
+        <v>3.570103855076898</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.08180869517887805</v>
+        <v>0.02439970530162204</v>
       </c>
       <c r="E7" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -3617,10 +3892,10 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>3.145427618139728</v>
+        <v>4.590377211110264</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.533790141635227</v>
+        <v>0.3319651785960673</v>
       </c>
       <c r="E8" s="3" t="b">
         <v>0</v>
@@ -3638,10 +3913,10 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3.382541500565241</v>
+        <v>5.040443562928248</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.4959613541370369</v>
+        <v>0.2831728507535727</v>
       </c>
       <c r="E9" s="3" t="b">
         <v>0</v>
@@ -3659,10 +3934,10 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8.501604050711201</v>
+        <v>9.31605390112334</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.0748386217510883</v>
+        <v>0.05366728320568032</v>
       </c>
       <c r="E10" s="3" t="b">
         <v>0</v>
@@ -3680,10 +3955,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>12.31515583821576</v>
+        <v>12.88096927941653</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.01515528027390947</v>
+        <v>0.01187228421098618</v>
       </c>
       <c r="E11" s="3" t="b">
         <v>1</v>
@@ -3697,14 +3972,14 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Welch ANOVA</t>
+          <t>Kruskal-Wallis</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1.55901690005224</v>
+        <v>7.455225220291108</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.2311011063970209</v>
+        <v>0.1136999556090968</v>
       </c>
       <c r="E12" s="3" t="b">
         <v>0</v>
@@ -3722,10 +3997,10 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>17.67933354192744</v>
+        <v>19.29097155501209</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.001425482501238332</v>
+        <v>0.0006889444971430368</v>
       </c>
       <c r="E13" s="3" t="b">
         <v>1</v>

--- a/app/analysis/results.xlsx
+++ b/app/analysis/results.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:Q57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3015,6 +3015,611 @@
       </c>
       <c r="Q46" s="3" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>CS0</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O47" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P47" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q47" s="3" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>CS1</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>146</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="P48" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q48" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>323</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M49" s="3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q49" s="3" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q50" s="3" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O51" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q51" s="3" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>CS0</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N52" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O52" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P52" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q52" s="3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>CS1</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>192</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q53" s="3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P54" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q54" s="3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>234</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M55" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="N55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q55" s="3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M56" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N56" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O56" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="P56" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q56" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>CS0</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K57" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P57" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q57" s="3" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -3228,22 +3833,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>41.4</v>
+        <v>40</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>11.85</v>
+        <v>11.22</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>116</v>
+        <v>109.83</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>36.62</v>
+        <v>36.28</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>14</v>
+        <v>13.17</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>4.45</v>
+        <v>4.49</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0</v>
@@ -3252,70 +3857,70 @@
         <v>0</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>2.41</v>
+        <v>2.68</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>4</v>
+        <v>4.58</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>0.7</v>
+        <v>0.83</v>
       </c>
       <c r="U2" s="3" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="W2" s="3" t="n">
         <v>0.21</v>
       </c>
       <c r="X2" s="3" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="Z2" s="3" t="n">
         <v>0.27</v>
       </c>
       <c r="AA2" s="3" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>3.89</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="3">
@@ -3325,94 +3930,94 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>50.89</v>
+        <v>53.09</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>15.43</v>
+        <v>15.45</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>139.11</v>
+        <v>151.45</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>49</v>
+        <v>73.25</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>17</v>
+        <v>17.55</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6.32</v>
+        <v>7.05</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.89</v>
+        <v>1.27</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.6</v>
+        <v>1.35</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2.67</v>
+        <v>3.09</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>1.58</v>
+        <v>2.81</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>4.67</v>
+        <v>5.55</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>3.12</v>
+        <v>5.45</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>2.11</v>
+        <v>2.82</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>1.05</v>
+        <v>2.56</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>3.89</v>
+        <v>5.36</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>2.09</v>
+        <v>5.2</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>0.87</v>
+        <v>1.75</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="W3" s="3" t="n">
         <v>0.18</v>
       </c>
       <c r="X3" s="3" t="n">
-        <v>0.11</v>
+        <v>0.27</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="AA3" s="3" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>10.22</v>
+        <v>10.73</v>
       </c>
       <c r="AC3" s="3" t="n">
-        <v>4.38</v>
+        <v>4.1</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>13.33</v>
+        <v>14.55</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>6.24</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="4">
@@ -3422,22 +4027,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>40.5</v>
+        <v>41.64</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>10.35</v>
+        <v>9.99</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>97.38</v>
+        <v>106.09</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>28.4</v>
+        <v>32.49</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>11.62</v>
+        <v>12.73</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>3.62</v>
+        <v>4.15</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>0</v>
@@ -3446,70 +4051,70 @@
         <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.71</v>
+        <v>1.27</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1</v>
+        <v>1.64</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1.07</v>
+        <v>1.75</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>1.88</v>
+        <v>3</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>2.03</v>
+        <v>3.22</v>
       </c>
       <c r="P4" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q4" s="3" t="n">
         <v>1.38</v>
       </c>
-      <c r="Q4" s="3" t="n">
-        <v>1.19</v>
-      </c>
       <c r="R4" s="3" t="n">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0.62</v>
+        <v>0.91</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>0.52</v>
+        <v>0.83</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>0.89</v>
       </c>
       <c r="Z4" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AA4" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="AA4" s="3" t="n">
-        <v>0.23</v>
-      </c>
       <c r="AB4" s="3" t="n">
-        <v>8.880000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AC4" s="3" t="n">
-        <v>3.56</v>
+        <v>3.41</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>8.75</v>
+        <v>10.09</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>3.85</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="5">
@@ -3519,94 +4124,94 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>42.44</v>
+        <v>43.82</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>8.109999999999999</v>
+        <v>10.64</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>111.67</v>
+        <v>122.09</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>29.79</v>
+        <v>36.79</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>13.56</v>
+        <v>14.91</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>3.81</v>
+        <v>4.74</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>2.89</v>
+        <v>3.27</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.05</v>
+        <v>1.56</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>5.33</v>
+        <v>6.18</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>2.12</v>
+        <v>3.22</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>5.44</v>
+        <v>6.27</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.67</v>
+        <v>2.53</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="AA5" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>7.56</v>
+        <v>7.82</v>
       </c>
       <c r="AC5" s="3" t="n">
-        <v>2.51</v>
+        <v>2.68</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>13.22</v>
+        <v>12.82</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>4.09</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="6">
@@ -3616,94 +4221,94 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>65.11</v>
+        <v>63.45</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>26.23</v>
+        <v>24.8</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>168.11</v>
+        <v>168.55</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>86.88</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>20.78</v>
+        <v>20.82</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>10.81</v>
+        <v>10.31</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>6.67</v>
+        <v>6.82</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>5.85</v>
+        <v>6.23</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>2.56</v>
+        <v>2.91</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>2.19</v>
+        <v>2.63</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>4.78</v>
+        <v>5.55</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>4.02</v>
+        <v>5.07</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>0.11</v>
+        <v>0.27</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>0.33</v>
+        <v>0.65</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="AA6" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>13.56</v>
+        <v>13</v>
       </c>
       <c r="AC6" s="3" t="n">
-        <v>4.98</v>
+        <v>4.88</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>14.67</v>
+        <v>14.09</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>9.140000000000001</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3762,17 +4367,17 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Welch ANOVA</t>
+          <t>Kruskal-Wallis</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2.067175831394276</v>
+        <v>10.18610159789185</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.1253990966241199</v>
+        <v>0.03740683300986365</v>
       </c>
       <c r="E2" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3787,10 +4392,10 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2.030109204962793</v>
+        <v>2.659114096214747</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.1307841068053283</v>
+        <v>0.05727520453044141</v>
       </c>
       <c r="E3" s="3" t="b">
         <v>0</v>
@@ -3808,13 +4413,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2.10597923163696</v>
+        <v>2.89187999019953</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.1200168571318576</v>
+        <v>0.04345749314168366</v>
       </c>
       <c r="E4" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3829,10 +4434,10 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>7.455225220291108</v>
+        <v>9.257529982605492</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.1136999556090968</v>
+        <v>0.05497509935165682</v>
       </c>
       <c r="E5" s="3" t="b">
         <v>0</v>
@@ -3846,17 +4451,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Welch ANOVA</t>
+          <t>Kruskal-Wallis</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.175921966613092</v>
+        <v>6.958554221727665</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.01339961772467672</v>
+        <v>0.1380947221851084</v>
       </c>
       <c r="E6" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3867,17 +4472,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Welch ANOVA</t>
+          <t>Kruskal-Wallis</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3.570103855076898</v>
+        <v>6.351338070256944</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.02439970530162204</v>
+        <v>0.1744016264233088</v>
       </c>
       <c r="E7" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3892,10 +4497,10 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>4.590377211110264</v>
+        <v>3.309338521400775</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.3319651785960673</v>
+        <v>0.5074540134785934</v>
       </c>
       <c r="E8" s="3" t="b">
         <v>0</v>
@@ -3913,10 +4518,10 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>5.040443562928248</v>
+        <v>4.142698834430373</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.2831728507535727</v>
+        <v>0.387037998819581</v>
       </c>
       <c r="E9" s="3" t="b">
         <v>0</v>
@@ -3934,10 +4539,10 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>9.31605390112334</v>
+        <v>8.233114847534933</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.05366728320568032</v>
+        <v>0.08340261718171886</v>
       </c>
       <c r="E10" s="3" t="b">
         <v>0</v>
@@ -3955,10 +4560,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>12.88096927941653</v>
+        <v>18.29587555834582</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.01187228421098618</v>
+        <v>0.001080137135282424</v>
       </c>
       <c r="E11" s="3" t="b">
         <v>1</v>
@@ -3976,10 +4581,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>7.455225220291108</v>
+        <v>9.257529982605492</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.1136999556090968</v>
+        <v>0.05497509935165682</v>
       </c>
       <c r="E12" s="3" t="b">
         <v>0</v>
@@ -3997,10 +4602,10 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>19.29097155501209</v>
+        <v>25.45389143230871</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.0006889444971430368</v>
+        <v>4.076914655868158e-05</v>
       </c>
       <c r="E13" s="3" t="b">
         <v>1</v>
